--- a/ReturnOrders.xlsx
+++ b/ReturnOrders.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vinod\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFAB2D8D-15C4-4114-8BA5-0D31991FAFB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC687658-0BF2-429F-805F-1C42D16C1117}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7510,7 +7510,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O696"/>
@@ -7579,7 +7579,7 @@
         <v>2369</v>
       </c>
     </row>
-    <row r="2" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -7624,7 +7624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -7669,7 +7669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -7714,7 +7714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -7759,7 +7759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -7804,7 +7804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -7849,7 +7849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -7894,7 +7894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -7939,7 +7939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -7984,7 +7984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -8029,7 +8029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -8074,7 +8074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -8119,7 +8119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -8164,7 +8164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -8209,7 +8209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -8254,7 +8254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>14</v>
       </c>
@@ -8299,7 +8299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>14</v>
       </c>
@@ -8344,7 +8344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>14</v>
       </c>
@@ -8389,7 +8389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>14</v>
       </c>
@@ -8434,7 +8434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>14</v>
       </c>
@@ -8479,7 +8479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>14</v>
       </c>
@@ -8524,7 +8524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>14</v>
       </c>
@@ -8569,7 +8569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>14</v>
       </c>
@@ -8614,7 +8614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>14</v>
       </c>
@@ -8659,7 +8659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>14</v>
       </c>
@@ -8704,7 +8704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>14</v>
       </c>
@@ -8749,7 +8749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>14</v>
       </c>
@@ -8794,7 +8794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>14</v>
       </c>
@@ -8839,7 +8839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>14</v>
       </c>
@@ -8884,7 +8884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>14</v>
       </c>
@@ -8929,7 +8929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>14</v>
       </c>
@@ -8974,7 +8974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>14</v>
       </c>
@@ -9019,7 +9019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>14</v>
       </c>
@@ -9064,7 +9064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>14</v>
       </c>
@@ -9109,7 +9109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>14</v>
       </c>
@@ -9154,7 +9154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>14</v>
       </c>
@@ -9199,7 +9199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>14</v>
       </c>
@@ -9244,7 +9244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>14</v>
       </c>
@@ -9289,7 +9289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>14</v>
       </c>
@@ -9334,7 +9334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>14</v>
       </c>
@@ -9379,7 +9379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>14</v>
       </c>
@@ -9424,7 +9424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>14</v>
       </c>
@@ -9469,7 +9469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>14</v>
       </c>
@@ -9514,7 +9514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>14</v>
       </c>
@@ -9559,7 +9559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>14</v>
       </c>
@@ -9604,7 +9604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>14</v>
       </c>
@@ -9649,7 +9649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>14</v>
       </c>
@@ -9694,7 +9694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>14</v>
       </c>
@@ -9739,7 +9739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>14</v>
       </c>
@@ -9784,7 +9784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>14</v>
       </c>
@@ -9829,7 +9829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>14</v>
       </c>
@@ -9874,7 +9874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>14</v>
       </c>
@@ -9919,7 +9919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>14</v>
       </c>
@@ -9964,7 +9964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>14</v>
       </c>
@@ -10009,7 +10009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>14</v>
       </c>
@@ -10054,7 +10054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>14</v>
       </c>
@@ -10099,7 +10099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>14</v>
       </c>
@@ -10144,7 +10144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>14</v>
       </c>
@@ -10189,7 +10189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>14</v>
       </c>
@@ -10234,7 +10234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>14</v>
       </c>
@@ -10279,7 +10279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>14</v>
       </c>
@@ -10324,7 +10324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>14</v>
       </c>
@@ -10369,7 +10369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>14</v>
       </c>
@@ -10414,7 +10414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>14</v>
       </c>
@@ -10459,7 +10459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>14</v>
       </c>
@@ -10504,7 +10504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>14</v>
       </c>
@@ -10549,7 +10549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>14</v>
       </c>
@@ -10594,7 +10594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>14</v>
       </c>
@@ -10639,7 +10639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>14</v>
       </c>
@@ -10684,7 +10684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>14</v>
       </c>
@@ -10729,7 +10729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>14</v>
       </c>
@@ -10774,7 +10774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>14</v>
       </c>
@@ -10819,7 +10819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>14</v>
       </c>
@@ -10864,7 +10864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>14</v>
       </c>
@@ -10909,7 +10909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>14</v>
       </c>
@@ -10954,7 +10954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>14</v>
       </c>
@@ -10999,7 +10999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>14</v>
       </c>
@@ -11044,7 +11044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>14</v>
       </c>
@@ -11089,7 +11089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>14</v>
       </c>
@@ -11134,7 +11134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>14</v>
       </c>
@@ -11179,7 +11179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>14</v>
       </c>
@@ -11224,7 +11224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>14</v>
       </c>
@@ -11269,7 +11269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>14</v>
       </c>
@@ -11314,7 +11314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>14</v>
       </c>
@@ -11359,7 +11359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>14</v>
       </c>
@@ -11404,7 +11404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>14</v>
       </c>
@@ -11449,7 +11449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>14</v>
       </c>
@@ -11494,7 +11494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>14</v>
       </c>
@@ -11539,7 +11539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>14</v>
       </c>
@@ -11584,7 +11584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>14</v>
       </c>
@@ -11629,7 +11629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>14</v>
       </c>
@@ -11674,7 +11674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>14</v>
       </c>
@@ -11719,7 +11719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>14</v>
       </c>
@@ -11764,7 +11764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>14</v>
       </c>
@@ -11809,7 +11809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>14</v>
       </c>
@@ -11854,7 +11854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>14</v>
       </c>
@@ -11899,7 +11899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>14</v>
       </c>
@@ -11944,7 +11944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>14</v>
       </c>
@@ -11989,7 +11989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>14</v>
       </c>
@@ -12034,7 +12034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>14</v>
       </c>
@@ -12079,7 +12079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>14</v>
       </c>
@@ -12124,7 +12124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>14</v>
       </c>
@@ -12169,7 +12169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>14</v>
       </c>
@@ -12214,7 +12214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>14</v>
       </c>
@@ -12259,7 +12259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>14</v>
       </c>
@@ -12304,7 +12304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>14</v>
       </c>
@@ -12349,7 +12349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>14</v>
       </c>
@@ -12394,7 +12394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>14</v>
       </c>
@@ -12439,7 +12439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>14</v>
       </c>
@@ -12484,7 +12484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>14</v>
       </c>
@@ -12529,7 +12529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>14</v>
       </c>
@@ -12574,7 +12574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>14</v>
       </c>
@@ -12619,7 +12619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>14</v>
       </c>
@@ -12664,7 +12664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>14</v>
       </c>
@@ -12709,7 +12709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>14</v>
       </c>
@@ -12754,7 +12754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>14</v>
       </c>
@@ -12799,7 +12799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>14</v>
       </c>
@@ -12844,7 +12844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>14</v>
       </c>
@@ -12889,7 +12889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>14</v>
       </c>
@@ -12934,7 +12934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>14</v>
       </c>
@@ -12979,7 +12979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>14</v>
       </c>
@@ -13024,7 +13024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>14</v>
       </c>
@@ -13069,7 +13069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>14</v>
       </c>
@@ -13114,7 +13114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>14</v>
       </c>
@@ -13159,7 +13159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>14</v>
       </c>
@@ -13204,7 +13204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>14</v>
       </c>
@@ -13249,7 +13249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>14</v>
       </c>
@@ -13294,7 +13294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>14</v>
       </c>
@@ -13339,7 +13339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>14</v>
       </c>
@@ -13384,7 +13384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>14</v>
       </c>
@@ -13429,7 +13429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>14</v>
       </c>
@@ -13474,7 +13474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>14</v>
       </c>
@@ -13519,7 +13519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>14</v>
       </c>
@@ -13564,7 +13564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>14</v>
       </c>
@@ -13609,7 +13609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>14</v>
       </c>
@@ -13654,7 +13654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>14</v>
       </c>
@@ -13699,7 +13699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>14</v>
       </c>
@@ -13744,7 +13744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>14</v>
       </c>
@@ -13789,7 +13789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>14</v>
       </c>
@@ -13834,7 +13834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>14</v>
       </c>
@@ -13879,7 +13879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>14</v>
       </c>
@@ -13924,7 +13924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>14</v>
       </c>
@@ -13969,7 +13969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>14</v>
       </c>
@@ -14014,7 +14014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>14</v>
       </c>
@@ -14059,7 +14059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>14</v>
       </c>
@@ -14104,7 +14104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>14</v>
       </c>
@@ -14149,7 +14149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>14</v>
       </c>
@@ -14191,7 +14191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>14</v>
       </c>
@@ -14233,7 +14233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>14</v>
       </c>
@@ -14275,7 +14275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>14</v>
       </c>
@@ -14317,7 +14317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>14</v>
       </c>
@@ -14359,7 +14359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>14</v>
       </c>
@@ -14401,7 +14401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>14</v>
       </c>
@@ -14443,7 +14443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>14</v>
       </c>
@@ -14485,7 +14485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>14</v>
       </c>
@@ -14527,7 +14527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>14</v>
       </c>
@@ -14569,7 +14569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>14</v>
       </c>
@@ -14611,7 +14611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>14</v>
       </c>
@@ -14653,7 +14653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>14</v>
       </c>
@@ -14695,7 +14695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>14</v>
       </c>
@@ -14737,7 +14737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>14</v>
       </c>
@@ -14779,7 +14779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>14</v>
       </c>
@@ -14821,7 +14821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>14</v>
       </c>
@@ -14863,7 +14863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>14</v>
       </c>
@@ -14905,7 +14905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>14</v>
       </c>
@@ -14947,7 +14947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>14</v>
       </c>
@@ -14989,7 +14989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>14</v>
       </c>
@@ -15031,7 +15031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>14</v>
       </c>
@@ -15073,7 +15073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>14</v>
       </c>
@@ -15115,7 +15115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>14</v>
       </c>
@@ -15157,7 +15157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>14</v>
       </c>
@@ -15199,7 +15199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>14</v>
       </c>
@@ -15241,7 +15241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>14</v>
       </c>
@@ -15283,7 +15283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>14</v>
       </c>
@@ -15325,7 +15325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>14</v>
       </c>
@@ -15367,7 +15367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>14</v>
       </c>
@@ -15409,7 +15409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>14</v>
       </c>
@@ -15451,7 +15451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>14</v>
       </c>
@@ -15493,7 +15493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>14</v>
       </c>
@@ -15535,7 +15535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>14</v>
       </c>
@@ -15577,7 +15577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>14</v>
       </c>
@@ -15619,7 +15619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>14</v>
       </c>
@@ -15661,7 +15661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>14</v>
       </c>
@@ -15703,7 +15703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>14</v>
       </c>
@@ -15745,7 +15745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>14</v>
       </c>
@@ -15787,7 +15787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>14</v>
       </c>
@@ -15829,7 +15829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>14</v>
       </c>
@@ -15871,7 +15871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>14</v>
       </c>
@@ -16003,7 +16003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>698</v>
       </c>
@@ -16048,7 +16048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>698</v>
       </c>
@@ -16093,7 +16093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>698</v>
       </c>
@@ -16138,7 +16138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>698</v>
       </c>
@@ -16180,7 +16180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>698</v>
       </c>
@@ -16222,7 +16222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>698</v>
       </c>
@@ -16264,7 +16264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>698</v>
       </c>
@@ -16306,7 +16306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>698</v>
       </c>
@@ -16348,7 +16348,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>698</v>
       </c>
@@ -16390,7 +16390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>698</v>
       </c>
@@ -16432,7 +16432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>698</v>
       </c>
@@ -16474,7 +16474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>698</v>
       </c>
@@ -16516,7 +16516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>698</v>
       </c>
@@ -16558,7 +16558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>698</v>
       </c>
@@ -16600,7 +16600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>698</v>
       </c>
@@ -16642,7 +16642,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>698</v>
       </c>
@@ -16684,7 +16684,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>698</v>
       </c>
@@ -16726,7 +16726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>698</v>
       </c>
@@ -16768,7 +16768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>698</v>
       </c>
@@ -16810,7 +16810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>698</v>
       </c>
@@ -16852,7 +16852,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>698</v>
       </c>
@@ -16894,7 +16894,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>698</v>
       </c>
@@ -16936,7 +16936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>698</v>
       </c>
@@ -16978,7 +16978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>698</v>
       </c>
@@ -17020,7 +17020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>698</v>
       </c>
@@ -17062,7 +17062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>698</v>
       </c>
@@ -17104,7 +17104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>698</v>
       </c>
@@ -17146,7 +17146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="219" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>698</v>
       </c>
@@ -17188,7 +17188,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>698</v>
       </c>
@@ -17230,7 +17230,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>698</v>
       </c>
@@ -17272,7 +17272,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>698</v>
       </c>
@@ -17314,7 +17314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>698</v>
       </c>
@@ -17356,7 +17356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>698</v>
       </c>
@@ -17398,7 +17398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>698</v>
       </c>
@@ -17440,7 +17440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>698</v>
       </c>
@@ -17482,7 +17482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>698</v>
       </c>
@@ -17524,7 +17524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>698</v>
       </c>
@@ -17566,7 +17566,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="229" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>698</v>
       </c>
@@ -17608,7 +17608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>698</v>
       </c>
@@ -17650,7 +17650,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="231" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>698</v>
       </c>
@@ -17692,7 +17692,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="232" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>698</v>
       </c>
@@ -17734,7 +17734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>698</v>
       </c>
@@ -17776,7 +17776,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>698</v>
       </c>
@@ -17818,7 +17818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>698</v>
       </c>
@@ -17860,7 +17860,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>698</v>
       </c>
@@ -17902,7 +17902,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="237" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>698</v>
       </c>
@@ -17944,7 +17944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>698</v>
       </c>
@@ -17986,7 +17986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>698</v>
       </c>
@@ -18028,7 +18028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>698</v>
       </c>
@@ -18070,7 +18070,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="241" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>698</v>
       </c>
@@ -18112,7 +18112,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="242" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>698</v>
       </c>
@@ -18154,7 +18154,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="243" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>698</v>
       </c>
@@ -18196,7 +18196,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="244" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>698</v>
       </c>
@@ -18238,7 +18238,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="245" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>698</v>
       </c>
@@ -18280,7 +18280,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="246" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>698</v>
       </c>
@@ -18322,7 +18322,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>698</v>
       </c>
@@ -18364,7 +18364,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="248" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>698</v>
       </c>
@@ -18406,7 +18406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>698</v>
       </c>
@@ -18448,7 +18448,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="250" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>698</v>
       </c>
@@ -18490,7 +18490,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="251" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>698</v>
       </c>
@@ -18532,7 +18532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>698</v>
       </c>
@@ -18574,7 +18574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>698</v>
       </c>
@@ -18616,7 +18616,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="254" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>698</v>
       </c>
@@ -18658,7 +18658,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="255" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>698</v>
       </c>
@@ -18700,7 +18700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>698</v>
       </c>
@@ -18742,7 +18742,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="257" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>698</v>
       </c>
@@ -18784,7 +18784,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="258" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>698</v>
       </c>
@@ -18826,7 +18826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="259" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>698</v>
       </c>
@@ -18868,7 +18868,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="260" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>698</v>
       </c>
@@ -18910,7 +18910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>698</v>
       </c>
@@ -18952,7 +18952,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="262" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>698</v>
       </c>
@@ -18994,7 +18994,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="263" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>698</v>
       </c>
@@ -19036,7 +19036,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="264" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>698</v>
       </c>
@@ -19078,7 +19078,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="265" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>698</v>
       </c>
@@ -19120,7 +19120,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="266" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>698</v>
       </c>
@@ -19162,7 +19162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>698</v>
       </c>
@@ -19204,7 +19204,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="268" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>698</v>
       </c>
@@ -19246,7 +19246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>698</v>
       </c>
@@ -19288,7 +19288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>698</v>
       </c>
@@ -19330,7 +19330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>698</v>
       </c>
@@ -19372,7 +19372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>698</v>
       </c>
@@ -19414,7 +19414,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="273" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>698</v>
       </c>
@@ -19456,7 +19456,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="274" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>698</v>
       </c>
@@ -19498,7 +19498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>698</v>
       </c>
@@ -19540,7 +19540,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="276" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>698</v>
       </c>
@@ -19582,7 +19582,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="277" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>698</v>
       </c>
@@ -19624,7 +19624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>698</v>
       </c>
@@ -19666,7 +19666,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="279" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>698</v>
       </c>
@@ -19708,7 +19708,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="280" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>698</v>
       </c>
@@ -19750,7 +19750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>698</v>
       </c>
@@ -19792,7 +19792,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="282" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>698</v>
       </c>
@@ -19834,7 +19834,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="283" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>698</v>
       </c>
@@ -19876,7 +19876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>698</v>
       </c>
@@ -19918,7 +19918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>698</v>
       </c>
@@ -19960,7 +19960,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="286" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>698</v>
       </c>
@@ -20002,7 +20002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>698</v>
       </c>
@@ -20044,7 +20044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>698</v>
       </c>
@@ -20086,7 +20086,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="289" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>698</v>
       </c>
@@ -20128,7 +20128,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="290" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>698</v>
       </c>
@@ -20170,7 +20170,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="291" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>698</v>
       </c>
@@ -20212,7 +20212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>698</v>
       </c>
@@ -20254,7 +20254,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="293" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>698</v>
       </c>
@@ -20296,7 +20296,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="294" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>698</v>
       </c>
@@ -20338,7 +20338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="295" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>698</v>
       </c>
@@ -20380,7 +20380,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="296" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>698</v>
       </c>
@@ -20422,7 +20422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>698</v>
       </c>
@@ -20464,7 +20464,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="298" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>698</v>
       </c>
@@ -20506,7 +20506,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="299" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>698</v>
       </c>
@@ -20548,7 +20548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>698</v>
       </c>
@@ -20590,7 +20590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="301" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>698</v>
       </c>
@@ -20632,7 +20632,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="302" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>698</v>
       </c>
@@ -20674,7 +20674,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="303" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>698</v>
       </c>
@@ -20716,7 +20716,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="304" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>698</v>
       </c>
@@ -20758,7 +20758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>698</v>
       </c>
@@ -20800,7 +20800,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="306" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>698</v>
       </c>
@@ -20842,7 +20842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>698</v>
       </c>
@@ -20884,7 +20884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>698</v>
       </c>
@@ -20926,7 +20926,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="309" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>698</v>
       </c>
@@ -20968,7 +20968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>698</v>
       </c>
@@ -21010,7 +21010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="311" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>698</v>
       </c>
@@ -21052,7 +21052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>698</v>
       </c>
@@ -21094,7 +21094,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="313" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>698</v>
       </c>
@@ -21136,7 +21136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>698</v>
       </c>
@@ -21178,7 +21178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>698</v>
       </c>
@@ -21220,7 +21220,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="316" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>698</v>
       </c>
@@ -21262,7 +21262,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="317" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>698</v>
       </c>
@@ -21304,7 +21304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>698</v>
       </c>
@@ -21346,7 +21346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>698</v>
       </c>
@@ -21388,7 +21388,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="320" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>698</v>
       </c>
@@ -21430,7 +21430,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="321" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>698</v>
       </c>
@@ -21472,7 +21472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>698</v>
       </c>
@@ -21514,7 +21514,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="323" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>698</v>
       </c>
@@ -21556,7 +21556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>698</v>
       </c>
@@ -21598,7 +21598,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="325" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>698</v>
       </c>
@@ -21640,7 +21640,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="326" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>698</v>
       </c>
@@ -21682,7 +21682,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="327" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>698</v>
       </c>
@@ -21724,7 +21724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>698</v>
       </c>
@@ -21766,7 +21766,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="329" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>698</v>
       </c>
@@ -21808,7 +21808,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="330" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>698</v>
       </c>
@@ -21850,7 +21850,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="331" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>698</v>
       </c>
@@ -21892,7 +21892,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="332" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>698</v>
       </c>
@@ -21934,7 +21934,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="333" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>698</v>
       </c>
@@ -21976,7 +21976,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="334" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>698</v>
       </c>
@@ -22018,7 +22018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="335" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>698</v>
       </c>
@@ -22060,7 +22060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="336" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>698</v>
       </c>
@@ -22102,7 +22102,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="337" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>698</v>
       </c>
@@ -22144,7 +22144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="338" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>698</v>
       </c>
@@ -22186,7 +22186,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="339" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>698</v>
       </c>
@@ -22228,7 +22228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="340" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>698</v>
       </c>
@@ -22270,7 +22270,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="341" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>698</v>
       </c>
@@ -22312,7 +22312,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="342" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>698</v>
       </c>
@@ -22354,7 +22354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>698</v>
       </c>
@@ -22396,7 +22396,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="344" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>698</v>
       </c>
@@ -22438,7 +22438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="345" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>698</v>
       </c>
@@ -22480,7 +22480,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="346" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>698</v>
       </c>
@@ -22522,7 +22522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="347" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>698</v>
       </c>
@@ -22564,7 +22564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="348" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>698</v>
       </c>
@@ -22606,7 +22606,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="349" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>698</v>
       </c>
@@ -22648,7 +22648,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="350" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>698</v>
       </c>
@@ -22690,7 +22690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="351" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>698</v>
       </c>
@@ -22732,7 +22732,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="352" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>698</v>
       </c>
@@ -22774,7 +22774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="353" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>698</v>
       </c>
@@ -22816,7 +22816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="354" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>698</v>
       </c>
@@ -22858,7 +22858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="355" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
         <v>12</v>
       </c>
@@ -22903,7 +22903,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="356" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
         <v>12</v>
       </c>
@@ -22948,7 +22948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="357" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
         <v>12</v>
       </c>
@@ -22993,7 +22993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="358" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
         <v>12</v>
       </c>
@@ -23038,7 +23038,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="359" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
         <v>12</v>
       </c>
@@ -23083,7 +23083,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="360" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
         <v>12</v>
       </c>
@@ -23128,7 +23128,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="361" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
         <v>12</v>
       </c>
@@ -23173,7 +23173,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="362" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
         <v>12</v>
       </c>
@@ -23218,7 +23218,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="363" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
         <v>12</v>
       </c>
@@ -23263,7 +23263,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="364" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
         <v>12</v>
       </c>
@@ -23308,7 +23308,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="365" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
         <v>12</v>
       </c>
@@ -23353,7 +23353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="366" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
         <v>12</v>
       </c>
@@ -23398,7 +23398,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="367" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
         <v>12</v>
       </c>
@@ -23443,7 +23443,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="368" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
         <v>12</v>
       </c>
@@ -23488,7 +23488,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="369" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
         <v>12</v>
       </c>
@@ -23533,7 +23533,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="370" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
         <v>12</v>
       </c>
@@ -23578,7 +23578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="371" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
         <v>12</v>
       </c>
@@ -23623,7 +23623,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="372" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
         <v>12</v>
       </c>
@@ -23668,7 +23668,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="373" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
         <v>12</v>
       </c>
@@ -23713,7 +23713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="374" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
         <v>12</v>
       </c>
@@ -23758,7 +23758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="375" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
         <v>12</v>
       </c>
@@ -23803,7 +23803,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="376" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
         <v>12</v>
       </c>
@@ -23848,7 +23848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="377" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
         <v>12</v>
       </c>
@@ -23893,7 +23893,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="378" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
         <v>12</v>
       </c>
@@ -23938,7 +23938,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="379" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
         <v>12</v>
       </c>
@@ -23983,7 +23983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="380" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
         <v>12</v>
       </c>
@@ -24028,7 +24028,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="381" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
         <v>12</v>
       </c>
@@ -24073,7 +24073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="382" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
         <v>12</v>
       </c>
@@ -24118,7 +24118,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="383" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
         <v>12</v>
       </c>
@@ -24163,7 +24163,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="384" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
         <v>12</v>
       </c>
@@ -24208,7 +24208,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="385" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
         <v>12</v>
       </c>
@@ -24253,7 +24253,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="386" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
         <v>12</v>
       </c>
@@ -24298,7 +24298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="387" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
         <v>12</v>
       </c>
@@ -24343,7 +24343,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="388" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
         <v>12</v>
       </c>
@@ -24388,7 +24388,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="389" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
         <v>12</v>
       </c>
@@ -24433,7 +24433,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="390" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
         <v>12</v>
       </c>
@@ -24478,7 +24478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="391" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
         <v>12</v>
       </c>
@@ -24523,7 +24523,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="392" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
         <v>12</v>
       </c>
@@ -24568,7 +24568,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="393" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
         <v>12</v>
       </c>
@@ -24613,7 +24613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="394" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
         <v>12</v>
       </c>
@@ -24658,7 +24658,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="395" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
         <v>12</v>
       </c>
@@ -24703,7 +24703,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="396" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
         <v>12</v>
       </c>
@@ -24748,7 +24748,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="397" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
         <v>12</v>
       </c>
@@ -24793,7 +24793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="398" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
         <v>12</v>
       </c>
@@ -24838,7 +24838,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="399" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
         <v>12</v>
       </c>
@@ -24883,7 +24883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="400" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
         <v>12</v>
       </c>
@@ -24928,7 +24928,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="401" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
         <v>12</v>
       </c>
@@ -24973,7 +24973,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="402" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
         <v>12</v>
       </c>
@@ -25018,7 +25018,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="403" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
         <v>12</v>
       </c>
@@ -25063,7 +25063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="404" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
         <v>12</v>
       </c>
@@ -25108,7 +25108,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="405" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
         <v>12</v>
       </c>
@@ -25153,7 +25153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="406" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
         <v>12</v>
       </c>
@@ -25198,7 +25198,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="407" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
         <v>12</v>
       </c>
@@ -25243,7 +25243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="408" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
         <v>12</v>
       </c>
@@ -25288,7 +25288,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="409" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
         <v>12</v>
       </c>
@@ -25333,7 +25333,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="410" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
         <v>12</v>
       </c>
@@ -25378,7 +25378,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="411" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
         <v>12</v>
       </c>
@@ -25423,7 +25423,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="412" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
         <v>12</v>
       </c>
@@ -25468,7 +25468,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="413" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
         <v>12</v>
       </c>
@@ -25513,7 +25513,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="414" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
         <v>12</v>
       </c>
@@ -25558,7 +25558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="415" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
         <v>12</v>
       </c>
@@ -25603,7 +25603,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="416" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
         <v>12</v>
       </c>
@@ -25648,7 +25648,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="417" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
         <v>12</v>
       </c>
@@ -25693,7 +25693,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="418" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
         <v>12</v>
       </c>
@@ -25738,7 +25738,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="419" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
         <v>12</v>
       </c>
@@ -25783,7 +25783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="420" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
         <v>12</v>
       </c>
@@ -25828,7 +25828,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="421" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
         <v>12</v>
       </c>
@@ -25873,7 +25873,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="422" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
         <v>12</v>
       </c>
@@ -25918,7 +25918,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="423" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
         <v>12</v>
       </c>
@@ -25963,7 +25963,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="424" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
         <v>12</v>
       </c>
@@ -26008,7 +26008,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="425" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
         <v>12</v>
       </c>
@@ -26053,7 +26053,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="426" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
         <v>12</v>
       </c>
@@ -26098,7 +26098,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="427" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
         <v>12</v>
       </c>
@@ -26143,7 +26143,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="428" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
         <v>12</v>
       </c>
@@ -26188,7 +26188,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="429" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
         <v>12</v>
       </c>
@@ -26233,7 +26233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="430" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
         <v>12</v>
       </c>
@@ -26278,7 +26278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="431" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
         <v>12</v>
       </c>
@@ -26323,7 +26323,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="432" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
         <v>12</v>
       </c>
@@ -26368,7 +26368,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="433" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
         <v>12</v>
       </c>
@@ -26413,7 +26413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="434" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
         <v>12</v>
       </c>
@@ -26458,7 +26458,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="435" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
         <v>12</v>
       </c>
@@ -26503,7 +26503,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="436" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
         <v>12</v>
       </c>
@@ -26548,7 +26548,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="437" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
         <v>12</v>
       </c>
@@ -26593,7 +26593,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="438" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
         <v>12</v>
       </c>
@@ -26638,7 +26638,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="439" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
         <v>12</v>
       </c>
@@ -26683,7 +26683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="440" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
         <v>12</v>
       </c>
@@ -26728,7 +26728,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="441" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
         <v>12</v>
       </c>
@@ -26773,7 +26773,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="442" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
         <v>12</v>
       </c>
@@ -26818,7 +26818,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="443" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
         <v>12</v>
       </c>
@@ -26863,7 +26863,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="444" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
         <v>12</v>
       </c>
@@ -26908,7 +26908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="445" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
         <v>12</v>
       </c>
@@ -26953,7 +26953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="446" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
         <v>12</v>
       </c>
@@ -26998,7 +26998,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="447" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
         <v>12</v>
       </c>
@@ -27043,7 +27043,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="448" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
         <v>12</v>
       </c>
@@ -27088,7 +27088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="449" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
         <v>12</v>
       </c>
@@ -27133,7 +27133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="450" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
         <v>12</v>
       </c>
@@ -27178,7 +27178,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="451" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
         <v>12</v>
       </c>
@@ -27223,7 +27223,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="452" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
         <v>12</v>
       </c>
@@ -27268,7 +27268,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="453" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
         <v>12</v>
       </c>
@@ -27313,7 +27313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="454" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
         <v>12</v>
       </c>
@@ -27358,7 +27358,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="455" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
         <v>12</v>
       </c>
@@ -27403,7 +27403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="456" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
         <v>12</v>
       </c>
@@ -27448,7 +27448,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="457" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
         <v>12</v>
       </c>
@@ -27493,7 +27493,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="458" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
         <v>12</v>
       </c>
@@ -27538,7 +27538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="459" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
         <v>12</v>
       </c>
@@ -27583,7 +27583,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="460" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
         <v>12</v>
       </c>
@@ -27628,7 +27628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="461" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
         <v>12</v>
       </c>
@@ -27673,7 +27673,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="462" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
         <v>12</v>
       </c>
@@ -27718,7 +27718,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="463" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
         <v>12</v>
       </c>
@@ -27763,7 +27763,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="464" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
         <v>12</v>
       </c>
@@ -27808,7 +27808,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="465" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
         <v>12</v>
       </c>
@@ -27853,7 +27853,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="466" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
         <v>12</v>
       </c>
@@ -27898,7 +27898,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="467" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
         <v>12</v>
       </c>
@@ -27943,7 +27943,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="468" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
         <v>12</v>
       </c>
@@ -27988,7 +27988,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="469" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A469" t="s">
         <v>12</v>
       </c>
@@ -28033,7 +28033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="470" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
         <v>12</v>
       </c>
@@ -28078,7 +28078,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="471" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
         <v>12</v>
       </c>
@@ -28123,7 +28123,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="472" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A472" t="s">
         <v>12</v>
       </c>
@@ -28168,7 +28168,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="473" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
         <v>12</v>
       </c>
@@ -28213,7 +28213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="474" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
         <v>12</v>
       </c>
@@ -28258,7 +28258,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="475" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
         <v>12</v>
       </c>
@@ -28303,7 +28303,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="476" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
         <v>12</v>
       </c>
@@ -28348,7 +28348,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="477" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
         <v>12</v>
       </c>
@@ -28393,7 +28393,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="478" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
         <v>12</v>
       </c>
@@ -28438,7 +28438,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="479" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
         <v>12</v>
       </c>
@@ -28483,7 +28483,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="480" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
         <v>12</v>
       </c>
@@ -28528,7 +28528,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="481" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
         <v>12</v>
       </c>
@@ -28573,7 +28573,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="482" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
         <v>12</v>
       </c>
@@ -28618,7 +28618,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="483" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
         <v>12</v>
       </c>
@@ -28663,7 +28663,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="484" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
         <v>12</v>
       </c>
@@ -28708,7 +28708,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="485" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A485" t="s">
         <v>12</v>
       </c>
@@ -28753,7 +28753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="486" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
         <v>12</v>
       </c>
@@ -28798,7 +28798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="487" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
         <v>12</v>
       </c>
@@ -28843,7 +28843,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="488" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
         <v>12</v>
       </c>
@@ -28888,7 +28888,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="489" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A489" t="s">
         <v>12</v>
       </c>
@@ -28933,7 +28933,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="490" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A490" t="s">
         <v>12</v>
       </c>
@@ -28978,7 +28978,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="491" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A491" t="s">
         <v>12</v>
       </c>
@@ -29023,7 +29023,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="492" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A492" t="s">
         <v>12</v>
       </c>
@@ -29068,7 +29068,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="493" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A493" t="s">
         <v>12</v>
       </c>
@@ -29113,7 +29113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="494" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A494" t="s">
         <v>12</v>
       </c>
@@ -29158,7 +29158,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="495" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A495" t="s">
         <v>12</v>
       </c>
@@ -29203,7 +29203,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="496" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A496" t="s">
         <v>12</v>
       </c>
@@ -29248,7 +29248,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="497" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A497" t="s">
         <v>12</v>
       </c>
@@ -29293,7 +29293,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="498" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A498" t="s">
         <v>12</v>
       </c>
@@ -29338,7 +29338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="499" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A499" t="s">
         <v>12</v>
       </c>
@@ -29383,7 +29383,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="500" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A500" t="s">
         <v>12</v>
       </c>
@@ -29428,7 +29428,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="501" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A501" t="s">
         <v>12</v>
       </c>
@@ -29473,7 +29473,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="502" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A502" t="s">
         <v>12</v>
       </c>
@@ -29518,7 +29518,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="503" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A503" t="s">
         <v>12</v>
       </c>
@@ -29563,7 +29563,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="504" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A504" t="s">
         <v>12</v>
       </c>
@@ -29608,7 +29608,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="505" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A505" t="s">
         <v>12</v>
       </c>
@@ -29653,7 +29653,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="506" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A506" t="s">
         <v>12</v>
       </c>
@@ -29698,7 +29698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="507" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A507" t="s">
         <v>12</v>
       </c>
@@ -29743,7 +29743,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="508" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A508" t="s">
         <v>12</v>
       </c>
@@ -29788,7 +29788,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="509" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A509" t="s">
         <v>12</v>
       </c>
@@ -29833,7 +29833,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="510" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A510" t="s">
         <v>12</v>
       </c>
@@ -29878,7 +29878,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="511" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A511" t="s">
         <v>12</v>
       </c>
@@ -29923,7 +29923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="512" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A512" t="s">
         <v>12</v>
       </c>
@@ -29968,7 +29968,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="513" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A513" t="s">
         <v>12</v>
       </c>
@@ -30013,7 +30013,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="514" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A514" t="s">
         <v>12</v>
       </c>
@@ -30058,7 +30058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="515" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A515" t="s">
         <v>12</v>
       </c>
@@ -30103,7 +30103,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="516" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A516" t="s">
         <v>12</v>
       </c>
@@ -30148,7 +30148,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="517" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A517" t="s">
         <v>12</v>
       </c>
@@ -30193,7 +30193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="518" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A518" t="s">
         <v>12</v>
       </c>
@@ -30238,7 +30238,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="519" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A519" t="s">
         <v>12</v>
       </c>
@@ -30283,7 +30283,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="520" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A520" t="s">
         <v>12</v>
       </c>
@@ -30328,7 +30328,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="521" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A521" t="s">
         <v>12</v>
       </c>
@@ -30373,7 +30373,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="522" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A522" t="s">
         <v>12</v>
       </c>
@@ -30418,7 +30418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="523" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A523" t="s">
         <v>12</v>
       </c>
@@ -30463,7 +30463,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="524" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A524" t="s">
         <v>12</v>
       </c>
@@ -30508,7 +30508,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="525" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A525" t="s">
         <v>12</v>
       </c>
@@ -30553,7 +30553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="526" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A526" t="s">
         <v>12</v>
       </c>
@@ -30598,7 +30598,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="527" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A527" t="s">
         <v>12</v>
       </c>
@@ -30643,7 +30643,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="528" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A528" t="s">
         <v>12</v>
       </c>
@@ -30688,7 +30688,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="529" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A529" t="s">
         <v>12</v>
       </c>
@@ -30733,7 +30733,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="530" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A530" t="s">
         <v>12</v>
       </c>
@@ -30778,7 +30778,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="531" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A531" t="s">
         <v>12</v>
       </c>
@@ -30823,7 +30823,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="532" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A532" t="s">
         <v>12</v>
       </c>
@@ -30868,7 +30868,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="533" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A533" t="s">
         <v>12</v>
       </c>
@@ -30913,7 +30913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="534" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A534" t="s">
         <v>12</v>
       </c>
@@ -30958,7 +30958,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="535" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A535" t="s">
         <v>12</v>
       </c>
@@ -31003,7 +31003,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="536" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A536" t="s">
         <v>12</v>
       </c>
@@ -31048,7 +31048,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="537" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A537" t="s">
         <v>12</v>
       </c>
@@ -31093,7 +31093,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="538" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A538" t="s">
         <v>12</v>
       </c>
@@ -31138,7 +31138,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="539" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A539" t="s">
         <v>12</v>
       </c>
@@ -31183,7 +31183,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="540" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A540" t="s">
         <v>12</v>
       </c>
@@ -31228,7 +31228,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="541" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A541" t="s">
         <v>12</v>
       </c>
@@ -31273,7 +31273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="542" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A542" t="s">
         <v>12</v>
       </c>
@@ -31318,7 +31318,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="543" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A543" t="s">
         <v>12</v>
       </c>
@@ -31363,7 +31363,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="544" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A544" t="s">
         <v>12</v>
       </c>
@@ -31408,7 +31408,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="545" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A545" t="s">
         <v>12</v>
       </c>
@@ -31453,7 +31453,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="546" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A546" t="s">
         <v>12</v>
       </c>
@@ -31498,7 +31498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="547" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A547" t="s">
         <v>12</v>
       </c>
@@ -31543,7 +31543,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="548" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A548" t="s">
         <v>12</v>
       </c>
@@ -31588,7 +31588,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="549" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A549" t="s">
         <v>12</v>
       </c>
@@ -31633,7 +31633,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="550" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A550" t="s">
         <v>12</v>
       </c>
@@ -31678,7 +31678,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="551" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A551" t="s">
         <v>12</v>
       </c>
@@ -31723,7 +31723,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="552" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A552" t="s">
         <v>12</v>
       </c>
@@ -31768,7 +31768,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="553" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A553" t="s">
         <v>12</v>
       </c>
@@ -31813,7 +31813,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="554" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A554" t="s">
         <v>12</v>
       </c>
@@ -31858,7 +31858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="555" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A555" t="s">
         <v>12</v>
       </c>
@@ -31903,7 +31903,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="556" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A556" t="s">
         <v>12</v>
       </c>
@@ -31948,7 +31948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="557" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A557" t="s">
         <v>12</v>
       </c>
@@ -31993,7 +31993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="558" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A558" t="s">
         <v>12</v>
       </c>
@@ -32038,7 +32038,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="559" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A559" t="s">
         <v>12</v>
       </c>
@@ -32083,7 +32083,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="560" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A560" t="s">
         <v>12</v>
       </c>
@@ -32128,7 +32128,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="561" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A561" t="s">
         <v>12</v>
       </c>
@@ -32173,7 +32173,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="562" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A562" t="s">
         <v>12</v>
       </c>
@@ -32218,7 +32218,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="563" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A563" t="s">
         <v>12</v>
       </c>
@@ -32263,7 +32263,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="564" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A564" t="s">
         <v>12</v>
       </c>
@@ -32308,7 +32308,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="565" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A565" t="s">
         <v>12</v>
       </c>
@@ -32353,7 +32353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="566" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A566" t="s">
         <v>12</v>
       </c>
@@ -32398,7 +32398,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="567" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A567" t="s">
         <v>12</v>
       </c>
@@ -32443,7 +32443,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="568" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A568" t="s">
         <v>12</v>
       </c>
@@ -32488,7 +32488,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="569" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A569" t="s">
         <v>12</v>
       </c>
@@ -32533,7 +32533,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="570" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A570" t="s">
         <v>12</v>
       </c>
@@ -32578,7 +32578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="571" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A571" t="s">
         <v>12</v>
       </c>
@@ -32623,7 +32623,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="572" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A572" t="s">
         <v>12</v>
       </c>
@@ -32668,7 +32668,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="573" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A573" t="s">
         <v>12</v>
       </c>
@@ -32713,7 +32713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="574" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A574" t="s">
         <v>12</v>
       </c>
@@ -32758,7 +32758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="575" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A575" t="s">
         <v>12</v>
       </c>
@@ -32803,7 +32803,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="576" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A576" t="s">
         <v>12</v>
       </c>
@@ -32848,7 +32848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="577" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A577" t="s">
         <v>12</v>
       </c>
@@ -32893,7 +32893,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="578" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A578" t="s">
         <v>12</v>
       </c>
@@ -32938,7 +32938,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="579" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A579" t="s">
         <v>12</v>
       </c>
@@ -32983,7 +32983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="580" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A580" t="s">
         <v>12</v>
       </c>
@@ -33028,7 +33028,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="581" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A581" t="s">
         <v>12</v>
       </c>
@@ -33073,7 +33073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="582" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A582" t="s">
         <v>12</v>
       </c>
@@ -33118,7 +33118,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="583" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A583" t="s">
         <v>12</v>
       </c>
@@ -33163,7 +33163,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="584" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A584" t="s">
         <v>12</v>
       </c>
@@ -33208,7 +33208,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="585" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A585" t="s">
         <v>12</v>
       </c>
@@ -33253,7 +33253,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="586" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A586" t="s">
         <v>12</v>
       </c>
@@ -33298,7 +33298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="587" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A587" t="s">
         <v>12</v>
       </c>
@@ -33343,7 +33343,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="588" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A588" t="s">
         <v>12</v>
       </c>
@@ -33388,7 +33388,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="589" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A589" t="s">
         <v>12</v>
       </c>
@@ -33433,7 +33433,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="590" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A590" t="s">
         <v>12</v>
       </c>
@@ -33478,7 +33478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="591" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A591" t="s">
         <v>12</v>
       </c>
@@ -33523,7 +33523,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="592" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A592" t="s">
         <v>12</v>
       </c>
@@ -33568,7 +33568,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="593" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A593" t="s">
         <v>12</v>
       </c>
@@ -33613,7 +33613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="594" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A594" t="s">
         <v>12</v>
       </c>
@@ -33658,7 +33658,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="595" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A595" t="s">
         <v>12</v>
       </c>
@@ -33703,7 +33703,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="596" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A596" t="s">
         <v>12</v>
       </c>
@@ -33748,7 +33748,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="597" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A597" t="s">
         <v>12</v>
       </c>
@@ -33793,7 +33793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="598" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A598" t="s">
         <v>12</v>
       </c>
@@ -33838,7 +33838,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="599" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A599" t="s">
         <v>12</v>
       </c>
@@ -33883,7 +33883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="600" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A600" t="s">
         <v>12</v>
       </c>
@@ -33928,7 +33928,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="601" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A601" t="s">
         <v>12</v>
       </c>
@@ -33973,7 +33973,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="602" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A602" t="s">
         <v>12</v>
       </c>
@@ -34018,7 +34018,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="603" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A603" t="s">
         <v>12</v>
       </c>
@@ -34063,7 +34063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="604" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A604" t="s">
         <v>12</v>
       </c>
@@ -34108,7 +34108,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="605" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A605" t="s">
         <v>12</v>
       </c>
@@ -34153,7 +34153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="606" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A606" t="s">
         <v>12</v>
       </c>
@@ -34198,7 +34198,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="607" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A607" t="s">
         <v>12</v>
       </c>
@@ -34243,7 +34243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="608" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A608" t="s">
         <v>12</v>
       </c>
@@ -34288,7 +34288,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="609" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A609" t="s">
         <v>12</v>
       </c>
@@ -34333,7 +34333,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="610" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A610" t="s">
         <v>12</v>
       </c>
@@ -34378,7 +34378,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="611" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A611" t="s">
         <v>12</v>
       </c>
@@ -34423,7 +34423,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="612" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A612" t="s">
         <v>12</v>
       </c>
@@ -34468,7 +34468,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="613" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A613" t="s">
         <v>12</v>
       </c>
@@ -34513,7 +34513,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="614" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A614" t="s">
         <v>12</v>
       </c>
@@ -34558,7 +34558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="615" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A615" t="s">
         <v>12</v>
       </c>
@@ -34603,7 +34603,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="616" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A616" t="s">
         <v>12</v>
       </c>
@@ -34648,7 +34648,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="617" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A617" t="s">
         <v>12</v>
       </c>
@@ -34693,7 +34693,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="618" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A618" t="s">
         <v>12</v>
       </c>
@@ -34738,7 +34738,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="619" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A619" t="s">
         <v>12</v>
       </c>
@@ -34783,7 +34783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="620" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A620" t="s">
         <v>12</v>
       </c>
@@ -34828,7 +34828,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="621" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A621" t="s">
         <v>12</v>
       </c>
@@ -34873,7 +34873,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="622" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A622" t="s">
         <v>12</v>
       </c>
@@ -34918,7 +34918,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="623" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A623" t="s">
         <v>12</v>
       </c>
@@ -34963,7 +34963,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="624" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A624" t="s">
         <v>12</v>
       </c>
@@ -35008,7 +35008,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="625" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A625" t="s">
         <v>12</v>
       </c>
@@ -35053,7 +35053,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="626" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A626" t="s">
         <v>12</v>
       </c>
@@ -35098,7 +35098,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="627" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A627" t="s">
         <v>12</v>
       </c>
@@ -35143,7 +35143,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="628" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A628" t="s">
         <v>12</v>
       </c>
@@ -35188,7 +35188,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="629" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A629" t="s">
         <v>12</v>
       </c>
@@ -35233,7 +35233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="630" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A630" t="s">
         <v>12</v>
       </c>
@@ -35278,7 +35278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="631" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A631" t="s">
         <v>12</v>
       </c>
@@ -35323,7 +35323,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="632" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A632" t="s">
         <v>12</v>
       </c>
@@ -35368,7 +35368,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="633" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A633" t="s">
         <v>12</v>
       </c>
@@ -35413,7 +35413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="634" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A634" t="s">
         <v>12</v>
       </c>
@@ -35458,7 +35458,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="635" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A635" t="s">
         <v>12</v>
       </c>
@@ -35503,7 +35503,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="636" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A636" t="s">
         <v>12</v>
       </c>
@@ -35548,7 +35548,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="637" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A637" t="s">
         <v>12</v>
       </c>
@@ -35593,7 +35593,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="638" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A638" t="s">
         <v>12</v>
       </c>
@@ -35638,7 +35638,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="639" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A639" t="s">
         <v>12</v>
       </c>
@@ -35683,7 +35683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="640" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A640" t="s">
         <v>12</v>
       </c>
@@ -35728,7 +35728,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="641" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A641" t="s">
         <v>12</v>
       </c>
@@ -35773,7 +35773,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="642" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A642" t="s">
         <v>12</v>
       </c>
@@ -35818,7 +35818,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="643" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A643" t="s">
         <v>12</v>
       </c>
@@ -35863,7 +35863,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="644" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A644" t="s">
         <v>12</v>
       </c>
@@ -35908,7 +35908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="645" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A645" t="s">
         <v>12</v>
       </c>
@@ -35953,7 +35953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="646" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A646" t="s">
         <v>12</v>
       </c>
@@ -35998,7 +35998,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="647" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A647" t="s">
         <v>12</v>
       </c>
@@ -36043,7 +36043,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="648" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A648" t="s">
         <v>12</v>
       </c>
@@ -36088,7 +36088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="649" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A649" t="s">
         <v>12</v>
       </c>
@@ -36133,7 +36133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="650" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A650" t="s">
         <v>12</v>
       </c>
@@ -36178,7 +36178,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="651" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A651" t="s">
         <v>12</v>
       </c>
@@ -36223,7 +36223,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="652" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A652" t="s">
         <v>12</v>
       </c>
@@ -36268,7 +36268,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="653" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A653" t="s">
         <v>12</v>
       </c>
@@ -36313,7 +36313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="654" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A654" t="s">
         <v>12</v>
       </c>
@@ -36358,7 +36358,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="655" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A655" t="s">
         <v>12</v>
       </c>
@@ -36403,7 +36403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="656" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A656" t="s">
         <v>12</v>
       </c>
@@ -36448,7 +36448,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="657" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A657" t="s">
         <v>12</v>
       </c>
@@ -36493,7 +36493,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="658" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A658" t="s">
         <v>12</v>
       </c>
@@ -36538,7 +36538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="659" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A659" t="s">
         <v>12</v>
       </c>
@@ -36583,7 +36583,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="660" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A660" t="s">
         <v>12</v>
       </c>
@@ -36628,7 +36628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="661" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A661" t="s">
         <v>12</v>
       </c>
@@ -36673,7 +36673,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="662" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A662" t="s">
         <v>12</v>
       </c>
@@ -36718,7 +36718,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="663" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A663" t="s">
         <v>12</v>
       </c>
@@ -36763,7 +36763,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="664" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A664" t="s">
         <v>12</v>
       </c>
@@ -36808,7 +36808,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="665" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A665" t="s">
         <v>12</v>
       </c>
@@ -36853,7 +36853,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="666" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A666" t="s">
         <v>12</v>
       </c>
@@ -36898,7 +36898,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="667" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A667" t="s">
         <v>12</v>
       </c>
@@ -36943,7 +36943,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="668" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A668" t="s">
         <v>12</v>
       </c>
@@ -36988,7 +36988,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="669" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A669" t="s">
         <v>12</v>
       </c>
@@ -37033,7 +37033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="670" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A670" t="s">
         <v>12</v>
       </c>
@@ -37078,7 +37078,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="671" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A671" t="s">
         <v>12</v>
       </c>
@@ -37123,7 +37123,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="672" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A672" t="s">
         <v>12</v>
       </c>
@@ -37168,7 +37168,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="673" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A673" t="s">
         <v>12</v>
       </c>
@@ -37213,7 +37213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="674" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A674" t="s">
         <v>12</v>
       </c>
@@ -37258,7 +37258,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="675" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A675" t="s">
         <v>12</v>
       </c>
@@ -37303,7 +37303,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="676" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A676" t="s">
         <v>12</v>
       </c>
@@ -37348,7 +37348,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="677" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A677" t="s">
         <v>12</v>
       </c>
@@ -37393,7 +37393,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="678" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A678" t="s">
         <v>12</v>
       </c>
@@ -37438,7 +37438,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="679" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A679" t="s">
         <v>12</v>
       </c>
@@ -37483,7 +37483,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="680" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A680" t="s">
         <v>12</v>
       </c>
@@ -37528,7 +37528,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="681" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A681" t="s">
         <v>12</v>
       </c>
@@ -37573,7 +37573,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="682" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A682" t="s">
         <v>12</v>
       </c>
@@ -37618,7 +37618,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="683" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A683" t="s">
         <v>12</v>
       </c>
@@ -37663,7 +37663,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="684" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A684" t="s">
         <v>12</v>
       </c>
@@ -37708,7 +37708,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="685" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A685" t="s">
         <v>12</v>
       </c>
@@ -37753,7 +37753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="686" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A686" t="s">
         <v>12</v>
       </c>
@@ -37798,7 +37798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="687" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A687" t="s">
         <v>12</v>
       </c>
@@ -37843,7 +37843,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="688" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A688" t="s">
         <v>12</v>
       </c>
@@ -37888,7 +37888,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="689" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A689" t="s">
         <v>12</v>
       </c>
@@ -37933,7 +37933,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="690" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A690" t="s">
         <v>12</v>
       </c>
@@ -37978,7 +37978,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="691" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A691" t="s">
         <v>12</v>
       </c>
@@ -38023,7 +38023,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="692" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A692" t="s">
         <v>12</v>
       </c>
@@ -38068,7 +38068,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="693" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A693" t="s">
         <v>12</v>
       </c>
@@ -38113,7 +38113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="694" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A694" t="s">
         <v>12</v>
       </c>
@@ -38158,7 +38158,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="695" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="695" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A695" t="s">
         <v>12</v>
       </c>
@@ -38203,7 +38203,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="696" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:15" x14ac:dyDescent="0.3">
       <c r="J696" s="2">
         <f>SUM(J2:J695)</f>
         <v>1703</v>
@@ -38222,14 +38222,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O696" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="S-SO-000216"/>
-        <filter val="S-SO-000568"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:O696" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
